--- a/Results/Study 2/VGG16 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 2/VGG16 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>380</v>
+        <v>513</v>
       </c>
       <c r="C2">
-        <v>260</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>196</v>
+        <v>483</v>
       </c>
       <c r="C3">
-        <v>444</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C2">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C3">
-        <v>97</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 2/VGG16 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 2/VGG16 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C2">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>483</v>
+        <v>412</v>
       </c>
       <c r="C3">
-        <v>157</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
